--- a/PO_TBD_20260616.xlsx
+++ b/PO_TBD_20260616.xlsx
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I75"/>
+  <dimension ref="A1:I85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -616,30 +616,30 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>CEFUROXIME 500MG ALTACEF GLENMARK</t>
+          <t>TAB UNASYN (SULTAMICILLIN) 375MG PFIZER</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>ALTACEF</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>tablet</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>48</v>
+        <v>159</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>1.47</v>
+        <v>4.07</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>70.56</v>
+        <v>647.13</v>
       </c>
     </row>
     <row r="11">
@@ -648,7 +648,7 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>TAB TREN (TRANEXAMIC ACID) 250MG</t>
+          <t>TAB MUCOSOLVAN (AMBROXOL) 30MG DKSH</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -665,13 +665,13 @@
         <v>0</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0</v>
+        <v>0.46</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12">
@@ -680,7 +680,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>LOCOA ( ESFLURBIPROFEN ) 40MG TRANSDERMAL PATCH 7'S</t>
+          <t>PROCTOSEDYL OINTMENT (FRAMYCETIN SULPHATE 1% W/W, HYDROCORTISONE 0.5% W/W, CINCHOCAINE.5% W/W, AESCULIN 1% W/W) 15G ZUELLIG PHARMA</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -690,20 +690,20 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>PACKET</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>66</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="13">
@@ -712,7 +712,7 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>CAP TRACIDOL (TRAMADOL) 50MG Y.S.P.</t>
+          <t>ORREPASTE (TRIAMCINOLONE ACETONIDE 0.1% W/W) 5G HOE</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -722,20 +722,20 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="E13" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>1.11</v>
+        <v>11.36</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>16.65</v>
+        <v>113.6</v>
       </c>
     </row>
     <row r="14">
@@ -744,7 +744,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>TAB ULTRACET (TRAMADOL 37.5MG/PARACETAMOL 325MG) J&amp;J</t>
+          <t>AXCEL UREA (UREA 10% W/W) CREAM 20G KOTRA PHARMA</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -754,20 +754,20 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="E14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>1.72</v>
+        <v>12</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>13.76</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15">
@@ -776,7 +776,7 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>TAB UNASYN (SULTAMICILLIN) 375MG PFIZER</t>
+          <t>INJ HYALGAN ( HYALURONIC ACID ) 20MG/2ML PE PHARMA</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -786,20 +786,20 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="E15" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>159</v>
+        <v>5</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>4.07</v>
+        <v>118</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>647.13</v>
+        <v>590</v>
       </c>
     </row>
     <row r="16">
@@ -808,7 +808,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>TAB CRESTOR ( ROSUVASTATIN ) 20MG ASTRAZENECA</t>
+          <t>SYR BENA EXPECTORANT(DIPHENHYDRAMINE 14MG, AMMONIUM CHLORIDE 135MG/5ML) 90ML XEPA</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -818,20 +818,20 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17">
@@ -840,7 +840,7 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>TAB PANTOPRAZOLE 40MG (GASTRO-RESISTANT) SANDOZ</t>
+          <t>DYFAZINE CREAM (SILVER SULPHADIAZINE 1%) 50G DYNAPHARM</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -850,20 +850,20 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="E17" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>0.55</v>
+        <v>13.64</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>26.4</v>
+        <v>136.4</v>
       </c>
     </row>
     <row r="18">
@@ -872,7 +872,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>SUSP CURAM (AMOXYCILLIN + CLAVULANIC ACID) 312.5MG/5ML 60ML SANDOZ</t>
+          <t>TAB APROVASC ( IRBESARTAN150MG / AMLODIPINE 5MG) SANOFI</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -882,20 +882,20 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>0</v>
+        <v>72.8</v>
       </c>
     </row>
     <row r="19">
@@ -904,7 +904,7 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>SYR NUROFEN (IBUPROFEN) 100MG/5ML 60ML RB HEALTH</t>
+          <t>INJ TACARLINE (ADRENALINE 1MG/ML) 1ML DUOPHARMA</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -914,20 +914,20 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>VIAL</t>
         </is>
       </c>
       <c r="E19" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G19" s="10" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>0</v>
+        <v>9.539999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -936,7 +936,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>SYR CHLORAMINE (CHLORPHENIRAMINE) 2.5MG/5ML 90ML DUOPHARMA</t>
+          <t>TAB COAPROVEL  (IRBESARTAN/HYDROCHLOROTHIAZIDE) 300MG/12.5MG SANOFI</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -946,20 +946,20 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>0</v>
+        <v>119.6</v>
       </c>
     </row>
     <row r="21">
@@ -968,7 +968,7 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>SUPP VOREN (DICLOFENAC SODIUM) 12.5MG Y.SP.</t>
+          <t>IVD HARTMANN'S SOLUTION 500ML B. BRAUN</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -978,20 +978,20 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>SUPPOSITORIES</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="E21" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="G21" s="10" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>0</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="22">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>PRISTINE SHAMPOO (KETOCONAZOLE 2%) 20MG 120ML XEPA</t>
+          <t>KEZORAL (KETOCONAZOLE 2% W/W) CREAM 15G DUOPHARMA</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -1010,20 +1010,20 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>17.2</v>
+        <v>7.7</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>17.2</v>
+        <v>92.40000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>TAB MUCOSOLVAN (AMBROXOL) 30MG DKSH</t>
+          <t>APPETON MV LYSINE SYRUP 120ML (VITAMIN A 1000IU + VITAMIN D3 200IU + VITAMIN B1 0.5MG + VITAMIN B2 0.5MG + VITAMIN B6 0.5MG + VITAMIN E 5IU + NICOTINAMIDE 6MG + PANTOTHENIC ACID 2MG + LYSINE 80MG) KOTRA PHARMA</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -1042,20 +1042,20 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E23" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="G23" s="10" t="n">
-        <v>0.46</v>
+        <v>39.04</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>30.82</v>
+        <v>390.4</v>
       </c>
     </row>
     <row r="24">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>SYR MUCOPROM (CARBOCISTEINE 100MG/ PROMETHAZINE 2.5MG /5ML) 90ML XEPA</t>
+          <t>LOZENGES DIFFLAM (BENZYDAMINE HYDROCHLORIDE 3MG) MINT FLAVOURED INOVA</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -1074,20 +1074,20 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>LOZENGES</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="H24" s="7" t="n">
-        <v>0</v>
+        <v>162</v>
       </c>
     </row>
     <row r="25">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>TAB ESOZ (ESOMEPRAZOLE) 40MG RANBAXY</t>
+          <t>SCABOMA LOTION  ( LINDANE 1% ) GLENMARK</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -1106,20 +1106,20 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E25" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>0</v>
+        <v>175</v>
       </c>
     </row>
     <row r="26">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>PROCTOSEDYL OINTMENT (FRAMYCETIN SULPHATE 1% W/W, HYDROCORTISONE 0.5% W/W, CINCHOCAINE.5% W/W, AESCULIN 1% W/W) 15G ZUELLIG PHARMA</t>
+          <t>TAB JARDIANCE ( EMPAGLIFLOZIN ) 25MG BOEHRINGER</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -1138,20 +1138,20 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E26" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>35</v>
+        <v>5.07</v>
       </c>
       <c r="H26" s="7" t="n">
-        <v>35</v>
+        <v>152.1</v>
       </c>
     </row>
     <row r="27">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>ORREPASTE (TRIAMCINOLONE ACETONIDE 0.1% W/W) 5G HOE</t>
+          <t>TABLET METGYL (METRONIDAZOLE) 400MG SM PHARMACEUTICALS</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -1170,20 +1170,20 @@
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E27" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>1</v>
+        <v>190</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>11.36</v>
+        <v>0.09</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>11.36</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="28">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>AXCEL UREA (UREA 10% W/W) CREAM 20G KOTRA PHARMA</t>
+          <t>INJ MENQUADFI (MENINGOCOCCAL VACCINE) 0.5ML 1D SANOFI</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>DOSE</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
@@ -1212,10 +1212,10 @@
         <v>1</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>12</v>
+        <v>97</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>12</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>INJ HYALGAN ( HYALURONIC ACID ) 20MG/2ML PE PHARMA</t>
+          <t>TAB EUTHYROX (LEVOTHYROXINE SODIUM) 100MCG MERCK</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
@@ -1234,20 +1234,20 @@
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E29" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="G29" s="10" t="n">
-        <v>118</v>
+        <v>0.53</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>236</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>IVD SODIUM LACTATE (HARTMANN SOLUTION) 500ML AIN MEDICARE</t>
+          <t>PNEUMOVAX 23 ( PNEUMOCOCCAL VACCINE POLYVALENT) MSD</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -1266,20 +1266,20 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>DOSE</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G30" s="7" t="n">
-        <v>0</v>
+        <v>106.5</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>0</v>
+        <v>532.5</v>
       </c>
     </row>
     <row r="31">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>SYR BENA EXPECTORANT(DIPHENHYDRAMINE 14MG, AMMONIUM CHLORIDE 135MG/5ML) 90ML XEPA</t>
+          <t>INJ GARASENT (GENTAMICIN SULPHATE  80MG/2ML AMP) DUOPHARMA</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -1298,20 +1298,20 @@
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>AMPULE</t>
         </is>
       </c>
       <c r="E31" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G31" s="10" t="n">
-        <v>3.4</v>
+        <v>2.35</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>23.8</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="32">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>DYFAZINE CREAM (SILVER SULPHADIAZINE 1%) 50G DYNAPHARM</t>
+          <t>CAP ESSENTIALSE MAX 600MG 30'S A.NATTERMANN &amp; CIE. GMBH</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E32" s="5" t="n">
@@ -1340,10 +1340,10 @@
         <v>1</v>
       </c>
       <c r="G32" s="7" t="n">
-        <v>13.64</v>
+        <v>0</v>
       </c>
       <c r="H32" s="7" t="n">
-        <v>13.64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>TAB APROVASC ( IRBESARTAN150MG / AMLODIPINE 5MG) SANOFI</t>
+          <t>EPIFLOR YOGURT POWDER WITH PROBIOTICS 2GX30 SACHETS MD PHARMA SDN BHD</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
@@ -1362,20 +1362,20 @@
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="E33" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G33" s="10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>INJ TACARLINE (ADRENALINE 1MG/ML) 1ML DUOPHARMA</t>
+          <t>TAB DEXALONE ( DEXAMETHASONE ) 0.5MG DUOPHARMA</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -1394,20 +1394,20 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>VIAL</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="G34" s="7" t="n">
-        <v>3.18</v>
+        <v>0.08</v>
       </c>
       <c r="H34" s="7" t="n">
-        <v>3.18</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="35">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>TAB COAPROVEL  (IRBESARTAN/HYDROCHLOROTHIAZIDE) 300MG/12.5MG SANOFI</t>
+          <t>SYR BUCANIL (TERBUTALINE SULPHATE 1.5MG/5ML) 100ML Y.S.P.</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
@@ -1426,20 +1426,20 @@
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E35" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G35" s="10" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>32.2</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="36">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>IVD HARTMANN'S SOLUTION 500ML B. BRAUN</t>
+          <t>SYR SEDILIX-RX LINCTUS (DEXTROMETHORPHAN 15MG/ PROMETHAZINE 3.125MG/ PHENYLEPHRINE 5MG EVERY 5ML)  90ML XEPA</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -1458,20 +1458,20 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G36" s="7" t="n">
-        <v>3.7</v>
+        <v>5.9</v>
       </c>
       <c r="H36" s="7" t="n">
-        <v>3.7</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="37">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>KEZORAL (KETOCONAZOLE 2% W/W) CREAM 15G DUOPHARMA</t>
+          <t>TAB GOUTRIC ( FEBUXOSTAT) NOVUGEN</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
@@ -1490,20 +1490,20 @@
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E37" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G37" s="10" t="n">
-        <v>7.7</v>
+        <v>4.74</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>15.4</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="38">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>ORS PLUS (TRISODIUM CITRATE 725MG, DEXTROSE ANHYDROUS 3375MG, SODIUM CHLORIDE 650MG, POTASSIUM CHLORIDE 375MG) SACHET PHARMANIAGA</t>
+          <t>S/C MOUNJARO (TIRZEPATIDE 25MG/ML) 2.5MG DOSE LILLY</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -1522,20 +1522,20 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>SACHET</t>
+          <t>DOSE</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G38" s="7" t="n">
-        <v>0.39</v>
+        <v>103.67</v>
       </c>
       <c r="H38" s="7" t="n">
-        <v>7.41</v>
+        <v>1347.71</v>
       </c>
     </row>
     <row r="39">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>APPETON MV LYSINE SYRUP 120ML (VITAMIN A 1000IU + VITAMIN D3 200IU + VITAMIN B1 0.5MG + VITAMIN B2 0.5MG + VITAMIN B6 0.5MG + VITAMIN E 5IU + NICOTINAMIDE 6MG + PANTOTHENIC ACID 2MG + LYSINE 80MG) KOTRA PHARMA</t>
+          <t>TAB CLARINASE (PSEUDOEPHEDRINE 120MG, LORATADINE 5MG) BAYER</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
@@ -1554,20 +1554,20 @@
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E39" s="8" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>1</v>
+        <v>180</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>39.04</v>
+        <v>1.81</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>39.04</v>
+        <v>325.8</v>
       </c>
     </row>
     <row r="40">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>LOZENGES DIFFLAM (BENZYDAMINE HYDROCHLORIDE 3MG) MINT FLAVOURED INOVA</t>
+          <t>CHEWABLE SIMCONE ( SIMETICONE ) 80MG IMEKS</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -1586,20 +1586,20 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>LOZENGES</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="G40" s="7" t="n">
-        <v>1.62</v>
+        <v>0.16</v>
       </c>
       <c r="H40" s="7" t="n">
-        <v>37.26</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>TAB PROBITOR ( OMEPRAZOLE ) 20MG SANDOZ</t>
+          <t>TAB SHINTAMET (CIMETIDINE) 400MG Y.S.P.</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
@@ -1622,16 +1622,16 @@
         </is>
       </c>
       <c r="E41" s="8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>21</v>
+        <v>180</v>
       </c>
       <c r="G41" s="10" t="n">
-        <v>0</v>
+        <v>0.58</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>0</v>
+        <v>104.4</v>
       </c>
     </row>
     <row r="42">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>CREAM LAMISIL (TERBINAFINE HYDROCHLORIDE) 10MG/G 15G ZUELLIG</t>
+          <t>TAB CONCOR (BISOPROLOL) 5MG MERCKS</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -1650,20 +1650,20 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>1</v>
+        <v>290</v>
       </c>
       <c r="G42" s="7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="H42" s="7" t="n">
-        <v>0</v>
+        <v>443.7</v>
       </c>
     </row>
     <row r="43">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>SCABOMA LOTION  ( LINDANE 1% ) GLENMARK</t>
+          <t>SMECTA (DIOSMECTITE 3G) ORANGE-VANILLA POWDER SACHETS ZUELLIG</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
@@ -1682,20 +1682,20 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>SACHET</t>
         </is>
       </c>
       <c r="E43" s="8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c r="G43" s="10" t="n">
-        <v>17.5</v>
+        <v>1.66</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>17.5</v>
+        <v>146.08</v>
       </c>
     </row>
     <row r="44">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>ZYNOMAX ( AZITHROMYCIN ) POWDER FOR ORAL SUSPENSION 200MG/5ML 20ML DUOPHARMA</t>
+          <t>TAB VELOXIN (MECLOZINE 25MG/PYRIDOXINE 50MG) PHARM-D</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -1714,20 +1714,20 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>2</v>
+        <v>90</v>
       </c>
       <c r="G44" s="7" t="n">
-        <v>12</v>
+        <v>1.06</v>
       </c>
       <c r="H44" s="7" t="n">
-        <v>24</v>
+        <v>95.40000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>WELLMEX ATOMIC ENEMA 20ML NGL TRADING</t>
+          <t>TAB STORVAS C (ATORVASTATIN) 20MG RANBAXY</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
@@ -1746,20 +1746,20 @@
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E45" s="8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="G45" s="10" t="n">
-        <v>2.68</v>
+        <v>0.68</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>5.36</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="46">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>TAB JARDIANCE ( EMPAGLIFLOZIN ) 25MG BOEHRINGER</t>
+          <t>TAB DIAPO (DIAZEPAM) 5MG DUOPHARMA</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -1782,16 +1782,16 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="G46" s="7" t="n">
-        <v>5.07</v>
+        <v>1.44</v>
       </c>
       <c r="H46" s="7" t="n">
-        <v>40.56</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="47">
@@ -1800,30 +1800,30 @@
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>SYR CEFUROXIME-125 (125MG/5ML) 50ML AXCEL KOTRA PHARMA</t>
+          <t>TAB ZITHROMAX (AZITHROMYCIN) 250MG 6'S PFIZER</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>AXCEL</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>PACKET</t>
         </is>
       </c>
       <c r="E47" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="G47" s="10" t="n">
-        <v>21.2</v>
+        <v>42.4</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>21.2</v>
+        <v>2501.6</v>
       </c>
     </row>
     <row r="48">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>TABLET COZAAR XQ 5/50MG ORGANON</t>
+          <t>INJ METHYCOBAL (MECOBALAMIN B12) 500MCG 1ML VIAL EISAI</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
@@ -1842,20 +1842,20 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>VIAL</t>
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="G48" s="7" t="n">
-        <v>2.7</v>
+        <v>6.8</v>
       </c>
       <c r="H48" s="7" t="n">
-        <v>62.1</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="49">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>TABLET METGYL (METRONIDAZOLE) 400MG SM PHARMACEUTICALS</t>
+          <t>NASAL DROPS ILIADIN  0.025% DECONGESTANT (1-6 YEARS) P&amp;G</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
@@ -1874,20 +1874,20 @@
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E49" s="8" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="G49" s="10" t="n">
-        <v>0.09</v>
+        <v>10.94</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>4.23</v>
+        <v>87.52</v>
       </c>
     </row>
     <row r="50">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>INJ MENQUADFI (MENINGOCOCCAL VACCINE) 0.5ML 1D SANOFI</t>
+          <t>TAB PLAVIX (CLOPIDOGREL) 75MG SANOFI</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -1906,20 +1906,20 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>DOSE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="G50" s="7" t="n">
-        <v>97</v>
+        <v>6.94</v>
       </c>
       <c r="H50" s="7" t="n">
-        <v>97</v>
+        <v>430.28</v>
       </c>
     </row>
     <row r="51">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>TAB EUTHYROX (LEVOTHYROXINE SODIUM) 100MCG MERCK</t>
+          <t>TAB YASMIN (DROSPIRENONE 3MG/ ETHINYLESTRADIOL 0.03MG) BAYER</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
@@ -1942,16 +1942,16 @@
         </is>
       </c>
       <c r="E51" s="8" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="G51" s="10" t="n">
-        <v>0.53</v>
+        <v>2.33</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>53</v>
+        <v>48.93</v>
       </c>
     </row>
     <row r="52">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>PNEUMOVAX 23 ( PNEUMOCOCCAL VACCINE POLYVALENT) MSD</t>
+          <t>SYRUP NOVOMIN (DIMENHYDRINATE) 15MG/5ML 60ML (ORANGE FLV) XEPA</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
@@ -1970,20 +1970,20 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>DOSE</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G52" s="7" t="n">
-        <v>106.5</v>
+        <v>5.5</v>
       </c>
       <c r="H52" s="7" t="n">
-        <v>106.5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="53">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>TAB VOZAN (VONOPRAZAN) 20MG NOVUGEN</t>
+          <t>TAB NORMATEN (ATENOLOL) 100MG XEPA</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
@@ -2006,16 +2006,16 @@
         </is>
       </c>
       <c r="E53" s="8" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="G53" s="10" t="n">
-        <v>4.42</v>
+        <v>0.52</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>167.96</v>
+        <v>12.48</v>
       </c>
     </row>
     <row r="54">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>TAB ROSUVASTATIN 20MG SYNERRV</t>
+          <t>TAB COAPROVEL (IRBESARTAN/ HYDROCHOLOTHIAZIDE) 150MG/12.5MG SANOFI</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
@@ -2038,16 +2038,16 @@
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="G54" s="7" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="H54" s="7" t="n">
-        <v>0</v>
+        <v>43.68</v>
       </c>
     </row>
     <row r="55">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>TAB ATORVASTATIN 20MG SYNERRV</t>
+          <t>TAB NOVOMIN (DIMENHYDRINATE) 50MG XEPA</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
@@ -2070,16 +2070,16 @@
         </is>
       </c>
       <c r="E55" s="8" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>7</v>
+        <v>70</v>
       </c>
       <c r="G55" s="10" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="H55" s="10" t="n">
-        <v>0</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="56">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>TAB ZIOMYCIN (AZITHROMYCIN) 500MG SYNERRV</t>
+          <t>TAB ZENTEL (ALBENDAZOLE) 200MG 2'S HALEON</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -2098,20 +2098,20 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>PACKET</t>
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="G56" s="7" t="n">
-        <v>0</v>
+        <v>9.65</v>
       </c>
       <c r="H56" s="7" t="n">
-        <v>0</v>
+        <v>173.7</v>
       </c>
     </row>
     <row r="57">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>TAB ROSUVASTATIN 10MG SYNERRV</t>
+          <t>EFFERVESCENT ACETYLCYSTIENE (N-ACETYLCYSTIENE) 600MG 2'S SANDOZ</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
@@ -2130,20 +2130,20 @@
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>STRIP</t>
         </is>
       </c>
       <c r="E57" s="8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="H57" s="10" t="n">
-        <v>0</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="58">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>TAB ZIOMYCIN (AZITHROMYCIN) 250MG SYNERRV</t>
+          <t>TAB ROWATINEX ( PINENE 31MG, CAMPHENE 31MG, CINEOL 3MG, FENCHONE 4MG, BORNEOL 10MG, ANETHOL 4MG ) DCH AURIGA</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -2166,16 +2166,16 @@
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="G58" s="7" t="n">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="H58" s="7" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
     </row>
     <row r="59">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>TAB GLIT (PIOGLITAZONE) 30MG SYNERRV</t>
+          <t>CREAM CLODERM (CLOBETASOL 0.05% W/W) 15G HOE</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
@@ -2194,20 +2194,20 @@
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="E59" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F59" s="8" t="n">
         <v>7</v>
       </c>
       <c r="G59" s="10" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="H59" s="10" t="n">
-        <v>0</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="60">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>TAB GLIT (PIOGLITAZONE) 15MG SYNERRV</t>
+          <t>IVD N/S 0.9% 500ML B. BRAUN</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -2226,20 +2226,20 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G60" s="7" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="H60" s="7" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="61">
@@ -2248,30 +2248,30 @@
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>DYNA CALAMINE LOTION (CALAMINE POWDER 15% W/V / MENTHOL 0.15% W/V) 100ML DYNAPHARM (M)</t>
+          <t>ALLERGOCROM  (SODIUM CROMOGLYCATE ) 2% EYE DROPS 10ML PHARMAFORTE URSAPHARM</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PHARMAFORTE</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="E61" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G61" s="10" t="n">
-        <v>6.37</v>
+        <v>16.5</v>
       </c>
       <c r="H61" s="10" t="n">
-        <v>6.37</v>
+        <v>115.5</v>
       </c>
     </row>
     <row r="62">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>INJ GARASENT (GENTAMICIN SULPHATE  80MG/2ML AMP) DUOPHARMA</t>
+          <t>AQUA CREAM (PARAFFIN, WHITE SOFT CREAM) 500GM DUOPHARMA</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -2290,20 +2290,20 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>AMPULE</t>
+          <t>JAR</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G62" s="7" t="n">
-        <v>2.35</v>
+        <v>17</v>
       </c>
       <c r="H62" s="7" t="n">
-        <v>2.35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="63">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>TAB BELTAS (BILASTINE) 20MG GLENMARK</t>
+          <t>BABY DROPS 30ML( VITAMIN A 1333IU, VITAMIN D3 438IU, VITAMIN E 6.57IU, VITAMIN B1 218MCG, VITAMIN B2 336MCG, VITAMIN B6 108MCG, NICOTINAMIDE 2.15MG, TAURINE 15MG, L-LYSINE 20MG PER ML) APPETON</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
@@ -2322,20 +2322,20 @@
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E63" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="G63" s="10" t="n">
-        <v>0.8</v>
+        <v>43.29</v>
       </c>
       <c r="H63" s="10" t="n">
-        <v>30.4</v>
+        <v>389.61</v>
       </c>
     </row>
     <row r="64">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>CAP ESSENTIALSE MAX 600MG 30'S A.NATTERMANN &amp; CIE. GMBH</t>
+          <t>INJECSOL MgSO4 (Magnesium Sulfate 50% W/v 2.465G) 5ML VIAL AIN MEDICARE</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
@@ -2354,20 +2354,20 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>VIAL</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F64" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G64" s="7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H64" s="7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>EPIFLOR YOGURT POWDER WITH PROBIOTICS 2GX30 SACHETS MD PHARMA SDN BHD</t>
+          <t>INJ MALON ( METOCLOPRAMIDE ) 10MG/2ML DUOPHARMA</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
@@ -2386,20 +2386,20 @@
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>VIAL</t>
         </is>
       </c>
       <c r="E65" s="8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G65" s="10" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="H65" s="10" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="66">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>TAB DEXALONE ( DEXAMETHASONE ) 0.5MG DUOPHARMA</t>
+          <t>INJ AMINOPHYLLIN 250MG/10ML FRESENIUS</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
@@ -2418,20 +2418,20 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>VIAL</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G66" s="7" t="n">
-        <v>0.08</v>
+        <v>8.5</v>
       </c>
       <c r="H66" s="7" t="n">
-        <v>0.48</v>
+        <v>68</v>
       </c>
     </row>
     <row r="67">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>SYR BUCANIL (TERBUTALINE SULPHATE 1.5MG/5ML) 100ML Y.S.P.</t>
+          <t>INJ ACIPAN (ATROPINE SULPHATE) 1MG/ML 1ML DUOPHARMA</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
@@ -2450,20 +2450,20 @@
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>VIAL</t>
         </is>
       </c>
       <c r="E67" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G67" s="10" t="n">
-        <v>3.7</v>
+        <v>2.32</v>
       </c>
       <c r="H67" s="10" t="n">
-        <v>11.1</v>
+        <v>18.56</v>
       </c>
     </row>
     <row r="68">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>SYR SEDILIX-RX LINCTUS (DEXTROMETHORPHAN 15MG/ PROMETHAZINE 3.125MG/ PHENYLEPHRINE 5MG EVERY 5ML)  90ML XEPA</t>
+          <t>A SCABS ( PERMETHRIN 5% ) LOTION 30ML HOE</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
@@ -2486,16 +2486,16 @@
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G68" s="7" t="n">
-        <v>5.9</v>
+        <v>11.6</v>
       </c>
       <c r="H68" s="7" t="n">
-        <v>5.9</v>
+        <v>104.4</v>
       </c>
     </row>
     <row r="69">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>TAB GOUTRIC ( FEBUXOSTAT) NOVUGEN</t>
+          <t>T3 MYCIN LOTION (CLINDAMYCIN PHOSPHATE 1%) 30ML HOE</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
@@ -2514,20 +2514,20 @@
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="E69" s="8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G69" s="10" t="n">
-        <v>4.74</v>
+        <v>27</v>
       </c>
       <c r="H69" s="10" t="n">
-        <v>23.7</v>
+        <v>243</v>
       </c>
     </row>
     <row r="70">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>S/C MOUNJARO (TIRZEPATIDE 25MG/ML) 2.5MG DOSE LILLY</t>
+          <t>KAOLIN-PECTIN (PECTIN 25MG/5ML, LIGHT KAOLIN 1G/5ML) 120ML DYNA</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
@@ -2546,48 +2546,368 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
+          <t>BOTTLE</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F70" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G70" s="7" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="H70" s="7" t="n">
+        <v>32.48</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="n">
+        <v>62</v>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>SUPP DIMENHYDRINATE 50MG DRIMINATE Y.S.P</t>
+        </is>
+      </c>
+      <c r="C71" s="8" t="inlineStr">
+        <is>
+          <t>DRIMINATE</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>SUPPOSITORIES</t>
+        </is>
+      </c>
+      <c r="E71" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F71" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G71" s="10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="H71" s="10" t="n">
+        <v>7.74</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>NITROSOL SUBLINGUAL AEROSOL SPRAY 400mcg/PER SPRAY VITAMODE</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>SPRAY</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G72" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="H72" s="7" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>INJ TYPHIM IV ( TYPHOID VACCINE ) SANOFI</t>
+        </is>
+      </c>
+      <c r="C73" s="8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D73" s="8" t="inlineStr">
+        <is>
           <t>DOSE</t>
         </is>
       </c>
-      <c r="E70" s="5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="F70" s="5" t="n">
+      <c r="E73" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F73" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="G70" s="7" t="n">
-        <v>103.67</v>
-      </c>
-      <c r="H70" s="7" t="n">
-        <v>311.01</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="11" t="inlineStr">
+      <c r="G73" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="H73" s="10" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>GENGIGEL SPRAY ( SODIUM HYALURONATE 0.01% ) 20ML PHARMANIAGA</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G74" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="H74" s="7" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="n">
+        <v>66</v>
+      </c>
+      <c r="B75" s="9" t="inlineStr">
+        <is>
+          <t>PREVENAR 13 (PNEUMOCOCCAL POLYSACCHARIDE CONJUGATE 13-VALENT) PFIZER</t>
+        </is>
+      </c>
+      <c r="C75" s="8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D75" s="8" t="inlineStr">
+        <is>
+          <t>DOSE</t>
+        </is>
+      </c>
+      <c r="E75" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G75" s="10" t="n">
+        <v>219</v>
+      </c>
+      <c r="H75" s="10" t="n">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>SYR DESTACURE ( DESLORATIDINE 2.5MG/5ML ) 60ML HEALOL</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>BOTTLE</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G76" s="7" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="H76" s="7" t="n">
+        <v>78.56999999999999</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="8" t="n">
+        <v>68</v>
+      </c>
+      <c r="B77" s="9" t="inlineStr">
+        <is>
+          <t>MONITAZONE (MOMETASONE FUROATE) 50MCG/ACTUATION NASAL SPRAY 140MD SHAMCHUNDANG PHARM</t>
+        </is>
+      </c>
+      <c r="C77" s="8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t>BOTTLE</t>
+        </is>
+      </c>
+      <c r="E77" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F77" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G77" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="H77" s="10" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>ENTEROGERMINA 2BCFU ORAL SUSPENSION 5ML OPELLA HEALTHCARE</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>BOX</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G78" s="7" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="H78" s="7" t="n">
+        <v>699.3</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="B79" s="9" t="inlineStr">
+        <is>
+          <t>INJ AMSUBAC (AMPICILLIN 1000MG/ SULBACTAM 500MG) 1.5 G AVERROES PHARMACEUTICALS SDN. BHD.</t>
+        </is>
+      </c>
+      <c r="C79" s="8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t>AMPULE</t>
+        </is>
+      </c>
+      <c r="E79" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F79" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G79" s="10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H79" s="10" t="n">
+        <v>59.2</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>TAB AUROXETIL 500 (Cefuroxime 500 Mg) Aurobindo Pharma</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>TABLET</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="n">
+        <v>450</v>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="G80" s="7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="H80" s="7" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="11" t="inlineStr">
         <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="H71" s="12" t="n">
-        <v>2359.03</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Total line items: 61</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Generated: 2026-06-16 08:03</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="13" t="inlineStr">
+      <c r="H81" s="12" t="n">
+        <v>14512.33</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Total line items: 71</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Generated: 2026-06-16 10:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="13" t="inlineStr">
         <is>
           <t>Note: Unit costs are from latest purchase price. Verify with supplier before confirming order.</t>
         </is>
@@ -2595,7 +2915,7 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A71:G71"/>
+    <mergeCell ref="A81:G81"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
